--- a/Draft_Windows-Build-Review-Methodology_FINAL.xlsx
+++ b/Draft_Windows-Build-Review-Methodology_FINAL.xlsx
@@ -570,7 +570,12 @@
 gpresult /h gpresult-cis-ms.html /f</s:t>
         </s:is>
       </s:c>
-      <s:c r="J3" s="2" t="n"/>
+      <s:c r="J3" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1046 - Network Service Discovery
+T1595.002 - Vulnerability Scanning</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K3" s="2" t="n"/>
       <s:c r="L3" s="2" t="n"/>
       <s:c r="M3" s="2" t="inlineStr">
@@ -623,7 +628,12 @@
 # Apply Domain Controllers OU GPO baseline from PDF</s:t>
         </s:is>
       </s:c>
-      <s:c r="J4" s="2" t="n"/>
+      <s:c r="J4" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1046 - Network Service Discovery
+T1595.002 - Vulnerability Scanning</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K4" s="2" t="n"/>
       <s:c r="L4" s="2" t="n"/>
       <s:c r="M4" s="2" t="inlineStr">
@@ -693,7 +703,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows\PowerShell\ScriptBlockLogging' -Name EnableScriptBlockLogging -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J6" s="2" t="n"/>
+      <s:c r="J6" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1059.001 - PowerShell
+T1562.002 - Disable Windows Event Logging</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K6" s="2" t="n"/>
       <s:c r="L6" s="2" t="n"/>
       <s:c r="M6" s="2" t="inlineStr">
@@ -744,7 +759,12 @@
           <s:t>Get-SmbServerConfiguration | Select-Object EnableSecuritySignature, RequireSecuritySignature, EnableSMB1Protocol</s:t>
         </s:is>
       </s:c>
-      <s:c r="J7" s="2" t="n"/>
+      <s:c r="J7" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1557.001 - Name Resolution Poisoning and SMB Relay
+T1021.002 - SMB/Windows Admin Shares</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K7" s="2" t="n"/>
       <s:c r="L7" s="2" t="n"/>
       <s:c r="M7" s="2" t="inlineStr">
@@ -795,7 +815,11 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows NT\DNSClient' -Name EnableMulticast -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J8" s="2" t="n"/>
+      <s:c r="J8" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1557.001 - Name Resolution Poisoning and SMB Relay</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K8" s="2" t="n"/>
       <s:c r="L8" s="2" t="n"/>
       <s:c r="M8" s="2" t="inlineStr">
@@ -846,7 +870,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows NT\DNSClient' -Name EnableNetbios -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J9" s="2" t="n"/>
+      <s:c r="J9" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1557.001 - Name Resolution Poisoning and SMB Relay
+T1040 - Network Sniffing</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K9" s="2" t="n"/>
       <s:c r="L9" s="2" t="n"/>
       <s:c r="M9" s="2" t="inlineStr">
@@ -897,7 +926,12 @@
           <s:t>Get-NetFirewallProfile -Profile Domain | Select-Object Name, Enabled, DefaultInboundAction, LogFileName</s:t>
         </s:is>
       </s:c>
-      <s:c r="J10" s="2" t="n"/>
+      <s:c r="J10" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1562.007 - Disable or Modify Cloud Firewall
+T1046 - Network Service Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K10" s="2" t="n"/>
       <s:c r="L10" s="2" t="n"/>
       <s:c r="M10" s="2" t="inlineStr">
@@ -950,7 +984,12 @@
 auditpol /get /subcategory:'Process Creation'</s:t>
         </s:is>
       </s:c>
-      <s:c r="J11" s="2" t="n"/>
+      <s:c r="J11" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1562.002 - Disable Windows Event Logging
+T1654 - Log Enumeration</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K11" s="2" t="n"/>
       <s:c r="L11" s="2" t="n"/>
       <s:c r="M11" s="2" t="inlineStr">
@@ -1001,7 +1040,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Microsoft\Cryptography\Wintrust\Config' -Name EnableCertPaddingCheck -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J12" s="2" t="n"/>
+      <s:c r="J12" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1553 - Subvert Trust Controls
+T1068 - Exploitation for Privilege Escalation</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K12" s="2" t="n"/>
       <s:c r="L12" s="2" t="n"/>
       <s:c r="M12" s="2" t="inlineStr">
@@ -1051,7 +1095,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Microsoft\Windows\CurrentVersion\Policies\LAPS' -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J13" s="2" t="n"/>
+      <s:c r="J13" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1078.002 - Domain Accounts
+T1552.001 - Credentials In Files</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K13" s="2" t="n"/>
       <s:c r="L13" s="2" t="n"/>
       <s:c r="M13" s="2" t="inlineStr">
@@ -1102,7 +1151,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Lsa\MSV1_0' -Name RestrictSendingNTLMTraffic -ErrorAction SilentlyContinue; Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Lsa' -Name LmCompatibilityLevel</s:t>
         </s:is>
       </s:c>
-      <s:c r="J14" s="2" t="n"/>
+      <s:c r="J14" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1550.002 - Pass the Hash
+T1556.004 - Network Device Authentication</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K14" s="2" t="n"/>
       <s:c r="L14" s="2" t="n"/>
       <s:c r="M14" s="2" t="inlineStr">
@@ -1153,7 +1207,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows\NetworkProvider\HardenedPaths' -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J15" s="2" t="n"/>
+      <s:c r="J15" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1021.002 - SMB/Windows Admin Shares
+T1187 - Forced Authentication</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K15" s="2" t="n"/>
       <s:c r="L15" s="2" t="n"/>
       <s:c r="M15" s="2" t="inlineStr">
@@ -1203,7 +1262,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Lsa' -Name RunAsPPL -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J16" s="2" t="n"/>
+      <s:c r="J16" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1003.001 - LSASS Memory
+T1562.001 - Disable or Modify Tools</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K16" s="2" t="n"/>
       <s:c r="L16" s="2" t="n"/>
       <s:c r="M16" s="2" t="inlineStr">
@@ -1254,7 +1318,12 @@
           <s:t>Get-MpComputerStatus | Select-Object AMServiceEnabled, AntivirusEnabled, RealTimeProtectionEnabled, IoavProtectionEnabled</s:t>
         </s:is>
       </s:c>
-      <s:c r="J17" s="2" t="n"/>
+      <s:c r="J17" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1562.001 - Disable or Modify Tools
+T1518.001 - Security Software Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K17" s="2" t="n"/>
       <s:c r="L17" s="2" t="n"/>
       <s:c r="M17" s="2" t="inlineStr">
@@ -1305,7 +1374,12 @@
           <s:t>net accounts; secedit /export /cfg $env:TEMP\secpol.cfg &amp; findstr /i Password lockout $env:TEMP\secpol.cfg</s:t>
         </s:is>
       </s:c>
-      <s:c r="J18" s="2" t="n"/>
+      <s:c r="J18" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1110 - Brute Force
+T1201 - Password Policy Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K18" s="2" t="n"/>
       <s:c r="L18" s="2" t="n"/>
       <s:c r="M18" s="2" t="inlineStr">
@@ -1375,7 +1449,12 @@
           <s:t>Get-Service Spooler | Select-Object Name, Status, StartType</s:t>
         </s:is>
       </s:c>
-      <s:c r="J20" s="2" t="n"/>
+      <s:c r="J20" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1210 - Exploitation of Remote Services
+T1489 - Service Stop</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K20" s="2" t="n"/>
       <s:c r="L20" s="2" t="n"/>
       <s:c r="M20" s="2" t="inlineStr">
@@ -1426,7 +1505,12 @@
           <s:t>Get-Service WebClient -ErrorAction SilentlyContinue | Select-Object Name, Status, StartType</s:t>
         </s:is>
       </s:c>
-      <s:c r="J21" s="2" t="n"/>
+      <s:c r="J21" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1187 - Forced Authentication
+T1210 - Exploitation of Remote Services</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K21" s="2" t="n"/>
       <s:c r="L21" s="2" t="n"/>
       <s:c r="M21" s="2" t="inlineStr">
@@ -1476,7 +1560,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Services\NTDS\Parameters' -Name LDAPServerIntegrity, LdapEnforceChannelBinding -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J22" s="2" t="n"/>
+      <s:c r="J22" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1040 - Network Sniffing
+T1087.002 - Domain Account</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K22" s="2" t="n"/>
       <s:c r="L22" s="2" t="n"/>
       <s:c r="M22" s="2" t="inlineStr">
@@ -1527,7 +1616,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Services\Netlogon\Parameters' -Name RequireSignOrSeal, VulnerableChannelAllowList -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J23" s="2" t="n"/>
+      <s:c r="J23" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1210 - Exploitation of Remote Services
+T1068 - Exploitation for Privilege Escalation</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K23" s="2" t="n"/>
       <s:c r="L23" s="2" t="n"/>
       <s:c r="M23" s="2" t="inlineStr">
@@ -1577,7 +1671,12 @@
           <s:t>Get-HotFix | Sort-Object InstalledOn -Descending | Select-Object -First 15 HotFixID, InstalledOn, Description</s:t>
         </s:is>
       </s:c>
-      <s:c r="J24" s="2" t="n"/>
+      <s:c r="J24" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1068 - Exploitation for Privilege Escalation
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K24" s="2" t="n"/>
       <s:c r="L24" s="2" t="n"/>
       <s:c r="M24" s="2" t="inlineStr">
@@ -1628,7 +1727,12 @@
           <s:t>Get-CimInstance Win32_OperatingSystem | Select-Object LastBootUpTime; Test-Path 'HKLM:\SOFTWARE\Microsoft\Windows\CurrentVersion\WindowsUpdate\Auto Update\RebootRequired'</s:t>
         </s:is>
       </s:c>
-      <s:c r="J25" s="2" t="n"/>
+      <s:c r="J25" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1068 - Exploitation for Privilege Escalation
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K25" s="2" t="n"/>
       <s:c r="L25" s="2" t="n"/>
       <s:c r="M25" s="2" t="inlineStr">
@@ -1697,7 +1801,12 @@
           <s:t>Get-Service Spooler -ErrorAction SilentlyContinue | Select-Object Status, StartType</s:t>
         </s:is>
       </s:c>
-      <s:c r="J27" s="2" t="n"/>
+      <s:c r="J27" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1210 - Exploitation of Remote Services
+T1489 - Service Stop</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K27" s="2" t="n"/>
       <s:c r="L27" s="2" t="n"/>
       <s:c r="M27" s="2" t="inlineStr">
@@ -1748,7 +1857,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows\WindowsUpdate' -ErrorAction SilentlyContinue; Get-ItemProperty 'HKLM:\SOFTWARE\Policies\Microsoft\Windows\WindowsUpdate\AU' -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J28" s="2" t="n"/>
+      <s:c r="J28" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1072 - Software Deployment Tools
+T1195.002 - Compromise Software Supply Chain</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K28" s="2" t="n"/>
       <s:c r="L28" s="2" t="n"/>
       <s:c r="M28" s="2" t="inlineStr">
@@ -1812,7 +1926,12 @@
           <s:t>whoami /priv</s:t>
         </s:is>
       </s:c>
-      <s:c r="J30" s="2" t="n"/>
+      <s:c r="J30" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1134 - Access Token Manipulation
+T1548 - Abuse Elevation Control Mechanism</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K30" s="2" t="n"/>
       <s:c r="L30" s="2" t="n"/>
       <s:c r="M30" s="2" t="inlineStr">
@@ -1857,7 +1976,12 @@
           <s:t>whoami /groups</s:t>
         </s:is>
       </s:c>
-      <s:c r="J31" s="2" t="n"/>
+      <s:c r="J31" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1069.001 - Local Groups
+T1078.003 - Local Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K31" s="2" t="n"/>
       <s:c r="L31" s="2" t="n"/>
       <s:c r="M31" s="2" t="n"/>
@@ -1898,7 +2022,12 @@
           <s:t>Get-CimInstance Win32_Service | Where-Object { Test-UnquotedServicePath $_.PathName } | Select-Object Name, PathName, StartName</s:t>
         </s:is>
       </s:c>
-      <s:c r="J32" s="2" t="n"/>
+      <s:c r="J32" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1574.009 - Path Interception by Unquoted Path
+T1543.003 - Windows Service</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K32" s="2" t="n"/>
       <s:c r="L32" s="2" t="n"/>
       <s:c r="M32" s="2" t="inlineStr">
@@ -1943,7 +2072,12 @@
           <s:t>Get-Acl 'C:\Program Files' | Select-Object -ExpandProperty Access</s:t>
         </s:is>
       </s:c>
-      <s:c r="J33" s="2" t="n"/>
+      <s:c r="J33" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1574.010 - Services File Permissions Weakness
+T1222.001 - Windows Permissions</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K33" s="2" t="n"/>
       <s:c r="L33" s="2" t="n"/>
       <s:c r="M33" s="2" t="n"/>
@@ -1984,7 +2118,12 @@
           <s:t>Get-ChildItem 'HKLM:\SYSTEM\CurrentControlSet\Services' | ForEach-Object { try { $acl = Get-Acl $_.PsPath; [PSCustomObject]@{ Key = $_.PSChildName; Risky = ($acl.Access | Where-Object { $_.IdentityReference -match 'Everyone|Users|Authenticated Users' -and $_.RegistryRights -match 'SetValue|FullControl' }) } } catch {} } | Where-Object { $_.Risky } | Select-Object -First 25</s:t>
         </s:is>
       </s:c>
-      <s:c r="J34" s="2" t="n"/>
+      <s:c r="J34" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1574.011 - Services Registry Permissions Weakness
+T1112 - Modify Registry</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K34" s="2" t="n"/>
       <s:c r="L34" s="2" t="n"/>
       <s:c r="M34" s="2" t="n"/>
@@ -2025,7 +2164,12 @@
           <s:t>Get-HotFix | Sort-Object InstalledOn -Descending | Select-Object -First 15 HotFixID, InstalledOn</s:t>
         </s:is>
       </s:c>
-      <s:c r="J35" s="2" t="n"/>
+      <s:c r="J35" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1068 - Exploitation for Privilege Escalation
+T1190 - Exploit Public-Facing Application</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K35" s="2" t="n"/>
       <s:c r="L35" s="2" t="n"/>
       <s:c r="M35" s="2" t="n"/>
@@ -2085,7 +2229,12 @@
           <s:t>reg query HKCU\Software\Microsoft\Windows\CurrentVersion\Run /s; reg query HKLM\Software\Microsoft\Windows\CurrentVersion\Run /s</s:t>
         </s:is>
       </s:c>
-      <s:c r="J37" s="2" t="n"/>
+      <s:c r="J37" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1547.001 - Registry Run Keys / Startup Folder
+T1112 - Modify Registry</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K37" s="2" t="n"/>
       <s:c r="L37" s="2" t="n"/>
       <s:c r="M37" s="2" t="inlineStr">
@@ -2130,7 +2279,12 @@
           <s:t>Get-ChildItem "$env:ProgramData\Microsoft\Windows\Start Menu\Programs\Startup", "$env:APPDATA\Microsoft\Windows\Start Menu\Programs\Startup" -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J38" s="2" t="n"/>
+      <s:c r="J38" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1547.001 - Registry Run Keys / Startup Folder
+T1037.001 - Logon Script (Windows)</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K38" s="2" t="n"/>
       <s:c r="L38" s="2" t="n"/>
       <s:c r="M38" s="2" t="n"/>
@@ -2171,7 +2325,12 @@
           <s:t>schtasks /query /fo LIST /v</s:t>
         </s:is>
       </s:c>
-      <s:c r="J39" s="2" t="n"/>
+      <s:c r="J39" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1053.005 - Scheduled Task
+T1543.003 - Windows Service</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K39" s="2" t="n"/>
       <s:c r="L39" s="2" t="n"/>
       <s:c r="M39" s="2" t="n"/>
@@ -2231,7 +2390,12 @@
           <s:t>Get-ChildItem "$env:ProgramData\Microsoft\Group Policy" -Recurse -Include Groups.xml -ErrorAction SilentlyContinue | Select-String "cpassword" | Select-Object -First 10</s:t>
         </s:is>
       </s:c>
-      <s:c r="J41" s="2" t="n"/>
+      <s:c r="J41" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1552.006 - Group Policy Preferences
+T1003.004 - LSA Secrets</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K41" s="2" t="n"/>
       <s:c r="L41" s="2" t="n"/>
       <s:c r="M41" s="2" t="n"/>
@@ -2272,7 +2436,12 @@
           <s:t>Get-ChildItem "$env:ProgramData","$env:USERPROFILE" -Recurse -Include *.config,*.xml,*.env,*.ps1 -ErrorAction SilentlyContinue | Select-String -Pattern "password|secret|token" -SimpleMatch:$false | Select-Object -First 20</s:t>
         </s:is>
       </s:c>
-      <s:c r="J42" s="2" t="n"/>
+      <s:c r="J42" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1552.001 - Credentials In Files
+T1083 - File and Directory Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K42" s="2" t="n"/>
       <s:c r="L42" s="2" t="n"/>
       <s:c r="M42" s="2" t="n"/>
@@ -2313,7 +2482,12 @@
           <s:t>@{ AWS = Test-Path "$env:USERPROFILE\.aws\credentials"; Azure = Test-Path "$env:USERPROFILE\.azure\azureProfile.json"; GCP = Test-Path "$env:USERPROFILE\AppData\Roaming\gcloud\credentials.db" }</s:t>
         </s:is>
       </s:c>
-      <s:c r="J43" s="2" t="n"/>
+      <s:c r="J43" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1552.001 - Credentials In Files
+T1528 - Steal Application Access Token</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K43" s="2" t="n"/>
       <s:c r="L43" s="2" t="n"/>
       <s:c r="M43" s="2" t="n"/>
@@ -2373,7 +2547,12 @@
           <s:t>net share</s:t>
         </s:is>
       </s:c>
-      <s:c r="J45" s="2" t="n"/>
+      <s:c r="J45" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1021.002 - SMB/Windows Admin Shares
+T1135 - Network Share Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K45" s="2" t="n"/>
       <s:c r="L45" s="2" t="n"/>
       <s:c r="M45" s="2" t="n"/>
@@ -2414,7 +2593,12 @@
           <s:t>net localgroup Administrators</s:t>
         </s:is>
       </s:c>
-      <s:c r="J46" s="2" t="n"/>
+      <s:c r="J46" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1078.003 - Local Accounts
+T1021.002 - SMB/Windows Admin Shares</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K46" s="2" t="n"/>
       <s:c r="L46" s="2" t="n"/>
       <s:c r="M46" s="2" t="n"/>
@@ -2474,7 +2658,12 @@
           <s:t>Get-NetFirewallRule -Enabled True | Select-Object DisplayName, Direction, Action, Profile | Select-Object -First 40</s:t>
         </s:is>
       </s:c>
-      <s:c r="J48" s="2" t="n"/>
+      <s:c r="J48" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1046 - Network Service Discovery
+T1016 - System Network Configuration Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K48" s="2" t="n"/>
       <s:c r="L48" s="2" t="n"/>
       <s:c r="M48" s="2" t="inlineStr">
@@ -2519,7 +2708,12 @@
           <s:t>Get-Acl C:\ | Select-Object -ExpandProperty Access</s:t>
         </s:is>
       </s:c>
-      <s:c r="J49" s="2" t="n"/>
+      <s:c r="J49" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1083 - File and Directory Discovery
+T1222.001 - Windows Permissions</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K49" s="2" t="n"/>
       <s:c r="L49" s="2" t="n"/>
       <s:c r="M49" s="2" t="n"/>
@@ -2560,7 +2754,12 @@
           <s:t>netsh winhttp show proxy</s:t>
         </s:is>
       </s:c>
-      <s:c r="J50" s="2" t="n"/>
+      <s:c r="J50" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1090.001 - Internal Proxy
+T1016 - System Network Configuration Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K50" s="2" t="n"/>
       <s:c r="L50" s="2" t="n"/>
       <s:c r="M50" s="2" t="n"/>
@@ -2620,7 +2819,12 @@
           <s:t>gpresult /r</s:t>
         </s:is>
       </s:c>
-      <s:c r="J52" s="2" t="n"/>
+      <s:c r="J52" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1615 - Group Policy Discovery
+T1484.001 - Group Policy Modification</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K52" s="2" t="n"/>
       <s:c r="L52" s="2" t="n"/>
       <s:c r="M52" s="2" t="inlineStr">
@@ -2670,7 +2874,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server' -Name fDenyTSConnections -ErrorAction SilentlyContinue; Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server\WinStations\RDP-Tcp' -Name UserAuthentication -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J53" s="2" t="n"/>
+      <s:c r="J53" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1021.001 - Remote Desktop Protocol
+T1563.002 - RDP Hijacking</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K53" s="2" t="n"/>
       <s:c r="L53" s="2" t="n"/>
       <s:c r="M53" s="2" t="inlineStr">
@@ -2715,7 +2924,12 @@
           <s:t>Get-LocalUser | Where-Object Enabled | Select-Object Name, LastLogon, PasswordLastSet</s:t>
         </s:is>
       </s:c>
-      <s:c r="J54" s="2" t="n"/>
+      <s:c r="J54" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1087.001 - Local Account
+T1078.003 - Local Accounts</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K54" s="2" t="n"/>
       <s:c r="L54" s="2" t="n"/>
       <s:c r="M54" s="2" t="n"/>
@@ -2756,7 +2970,12 @@
           <s:t>Get-ItemProperty 'HKLM:\Software\Microsoft\Windows\CurrentVersion\Uninstall\*' | Where-Object DisplayName | Select-Object DisplayName, DisplayVersion | Sort-Object DisplayName | Select-Object -First 50</s:t>
         </s:is>
       </s:c>
-      <s:c r="J55" s="2" t="n"/>
+      <s:c r="J55" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1518 - Software Discovery
+T1082 - System Information Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K55" s="2" t="n"/>
       <s:c r="L55" s="2" t="n"/>
       <s:c r="M55" s="2" t="n"/>
@@ -2797,7 +3016,12 @@
           <s:t>if (Get-Command Get-WindowsFeature -ErrorAction SilentlyContinue) { Get-WindowsFeature | Where-Object Installed | Select-Object Name, DisplayName } else { Get-WindowsOptionalFeature -Online | Where-Object State -eq Enabled | Select-Object FeatureName }</s:t>
         </s:is>
       </s:c>
-      <s:c r="J56" s="2" t="n"/>
+      <s:c r="J56" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1518 - Software Discovery
+T1082 - System Information Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K56" s="2" t="n"/>
       <s:c r="L56" s="2" t="n"/>
       <s:c r="M56" s="2" t="inlineStr">
@@ -2847,7 +3071,12 @@
           <s:t>try { Get-AppLockerPolicy -Effective -Xml | Out-String | Select-Object -First 1 } catch { 'AppLocker not configured or not available' }</s:t>
         </s:is>
       </s:c>
-      <s:c r="J57" s="2" t="n"/>
+      <s:c r="J57" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1480 - Execution Guardrails
+T1218 - System Binary Proxy Execution</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K57" s="2" t="n"/>
       <s:c r="L57" s="2" t="n"/>
       <s:c r="M57" s="2" t="inlineStr">
@@ -2897,7 +3126,12 @@
           <s:t>Get-CimInstance -Namespace root\Microsoft\Windows\DeviceGuard -ClassName DeviceGuard -ErrorAction SilentlyContinue | Select-Object SecurityServicesConfigured, SecurityServicesRunning, VirtualizationBasedSecurityStatus</s:t>
         </s:is>
       </s:c>
-      <s:c r="J58" s="2" t="n"/>
+      <s:c r="J58" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1003.001 - LSASS Memory
+T1055 - Process Injection</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K58" s="2" t="n"/>
       <s:c r="L58" s="2" t="n"/>
       <s:c r="M58" s="2" t="inlineStr">
@@ -2942,7 +3176,12 @@
           <s:t>nltest /dsgetdc:$env:USERDOMAIN 2&gt;&amp;1; (Get-CimInstance Win32_ComputerSystem).DomainRole</s:t>
         </s:is>
       </s:c>
-      <s:c r="J59" s="2" t="n"/>
+      <s:c r="J59" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1087.002 - Domain Account
+T1482 - Domain Trust Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K59" s="2" t="n"/>
       <s:c r="L59" s="2" t="n"/>
       <s:c r="M59" s="2" t="inlineStr">
@@ -2987,7 +3226,12 @@
           <s:t>w32tm /query /status</s:t>
         </s:is>
       </s:c>
-      <s:c r="J60" s="2" t="n"/>
+      <s:c r="J60" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1082 - System Information Discovery
+T1016 - System Network Configuration Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K60" s="2" t="n"/>
       <s:c r="L60" s="2" t="n"/>
       <s:c r="M60" s="2" t="n"/>
@@ -3028,7 +3272,12 @@
           <s:t>Get-DnsClientServerAddress -AddressFamily IPv4 | Select-Object InterfaceAlias, ServerAddresses</s:t>
         </s:is>
       </s:c>
-      <s:c r="J61" s="2" t="n"/>
+      <s:c r="J61" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1016 - System Network Configuration Discovery
+T1590.002 - DNS</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K61" s="2" t="n"/>
       <s:c r="L61" s="2" t="n"/>
       <s:c r="M61" s="2" t="n"/>
@@ -3069,7 +3318,12 @@
           <s:t>Get-WinEvent -LogName Security -MaxEvents 15 -ErrorAction SilentlyContinue | Select-Object TimeCreated, Id, LevelDisplayName, Message</s:t>
         </s:is>
       </s:c>
-      <s:c r="J62" s="2" t="n"/>
+      <s:c r="J62" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1654 - Log Enumeration
+T1070.001 - Clear Windows Event Logs</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K62" s="2" t="n"/>
       <s:c r="L62" s="2" t="n"/>
       <s:c r="M62" s="2" t="inlineStr">
@@ -3133,7 +3387,12 @@
           <s:t># Manual only: [Windows.Clipboard]::GetText() with customer approval</s:t>
         </s:is>
       </s:c>
-      <s:c r="J64" s="2" t="n"/>
+      <s:c r="J64" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1115 - Clipboard Data
+T1552.001 - Credentials In Files</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K64" s="2" t="n"/>
       <s:c r="L64" s="2" t="n"/>
       <s:c r="M64" s="2" t="inlineStr">
@@ -3197,7 +3456,12 @@
           <s:t>Get-ChildItem Env: | Select-Object Name, Value -First 30</s:t>
         </s:is>
       </s:c>
-      <s:c r="J66" s="2" t="n"/>
+      <s:c r="J66" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1082 - System Information Discovery
+T1552.001 - Credentials In Files</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K66" s="2" t="n"/>
       <s:c r="L66" s="2" t="n"/>
       <s:c r="M66" s="2" t="inlineStr">
@@ -3242,7 +3506,12 @@
           <s:t>Get-WinEvent -FilterHashtable @{ LogName='Application'; Id=1000,1001; StartTime=(Get-Date).AddDays(-30) } -MaxEvents 10</s:t>
         </s:is>
       </s:c>
-      <s:c r="J67" s="2" t="n"/>
+      <s:c r="J67" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1654 - Log Enumeration
+T1082 - System Information Discovery</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K67" s="2" t="n"/>
       <s:c r="L67" s="2" t="n"/>
       <s:c r="M67" s="2" t="n"/>
@@ -3288,7 +3557,12 @@
           <s:t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\CrashControl' -ErrorAction SilentlyContinue</s:t>
         </s:is>
       </s:c>
-      <s:c r="J68" s="2" t="n"/>
+      <s:c r="J68" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1003.001 - LSASS Memory
+T1552.001 - Credentials In Files</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K68" s="2" t="n"/>
       <s:c r="L68" s="2" t="n"/>
       <s:c r="M68" s="2" t="inlineStr">
@@ -3338,7 +3612,12 @@
           <s:t>Test-Path "C:\Windows\System32\bash.exe"; Test-Path "C:\Windows\System32\wsl.exe"</s:t>
         </s:is>
       </s:c>
-      <s:c r="J69" s="2" t="n"/>
+      <s:c r="J69" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1211 - Exploitation for Stealth
+T1059.003 - Windows Command Shell</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K69" s="2" t="n"/>
       <s:c r="L69" s="2" t="n"/>
       <s:c r="M69" s="2" t="inlineStr">
@@ -3402,7 +3681,12 @@
           <s:t>Get-WmiObject Win32_Service | Where-Object { $_.PathName -notmatch '"' }</s:t>
         </s:is>
       </s:c>
-      <s:c r="J71" s="2" t="n"/>
+      <s:c r="J71" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1574.009 - Path Interception by Unquoted Path
+T1543.003 - Windows Service</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K71" s="2" t="n"/>
       <s:c r="L71" s="2" t="n"/>
       <s:c r="M71" s="2" t="inlineStr">
@@ -3447,7 +3731,12 @@
           <s:t>Get-Acl "C:\Program Files"</s:t>
         </s:is>
       </s:c>
-      <s:c r="J72" s="2" t="n"/>
+      <s:c r="J72" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1574.010 - Services File Permissions Weakness
+T1222.001 - Windows Permissions</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K72" s="2" t="n"/>
       <s:c r="L72" s="2" t="n"/>
       <s:c r="M72" s="2" t="inlineStr">
@@ -3511,7 +3800,12 @@
           <s:t>Get-Acl C:\</s:t>
         </s:is>
       </s:c>
-      <s:c r="J74" s="2" t="n"/>
+      <s:c r="J74" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1083 - File and Directory Discovery
+T1222.001 - Windows Permissions</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K74" s="2" t="n"/>
       <s:c r="L74" s="2" t="n"/>
       <s:c r="M74" s="2" t="inlineStr">
@@ -3580,7 +3874,12 @@
           <s:t>reg query HKLM\SYSTEM\CurrentControlSet\Control\Lsa /v RunAsPPL</s:t>
         </s:is>
       </s:c>
-      <s:c r="J76" s="2" t="n"/>
+      <s:c r="J76" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1003.001 - LSASS Memory
+T1562.001 - Disable or Modify Tools</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K76" s="2" t="n"/>
       <s:c r="L76" s="2" t="n"/>
       <s:c r="M76" s="2" t="inlineStr">
@@ -3631,7 +3930,12 @@
           <s:t>net accounts</s:t>
         </s:is>
       </s:c>
-      <s:c r="J77" s="2" t="n"/>
+      <s:c r="J77" s="2" t="inlineStr">
+        <s:is>
+          <s:t>T1201 - Password Policy Discovery
+T1110 - Brute Force</s:t>
+        </s:is>
+      </s:c>
       <s:c r="K77" s="2" t="n"/>
       <s:c r="L77" s="2" t="n"/>
       <s:c r="M77" s="2" t="inlineStr">

--- a/Draft_Windows-Build-Review-Methodology_FINAL.xlsx
+++ b/Draft_Windows-Build-Review-Methodology_FINAL.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,8 +29,12 @@
     <font>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -40,6 +44,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00404040"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,7 +69,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -65,6 +79,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -431,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -450,90 +470,90 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>Scope</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Executor</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Executed</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="4" t="inlineStr">
         <is>
           <t>Comments</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="4" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="4" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="4" t="inlineStr">
         <is>
           <t>Tooling</t>
         </is>
       </c>
-      <c r="I1" s="3" t="inlineStr">
+      <c r="I1" s="4" t="inlineStr">
         <is>
           <t>Commands/Guidance</t>
         </is>
       </c>
-      <c r="J1" s="3" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>Mitre Technique</t>
         </is>
       </c>
-      <c r="K1" s="3" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>Policy</t>
         </is>
       </c>
-      <c r="L1" s="3" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>Written Issues</t>
         </is>
       </c>
-      <c r="M1" s="3" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="A2" s="5" t="n"/>
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>AUTOMATION</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n"/>
-      <c r="D2" s="1" t="n"/>
-      <c r="E2" s="1" t="n"/>
-      <c r="F2" s="1" t="n"/>
-      <c r="G2" s="1" t="n"/>
-      <c r="H2" s="1" t="n"/>
-      <c r="I2" s="1" t="n"/>
-      <c r="J2" s="1" t="n"/>
-      <c r="K2" s="1" t="n"/>
-      <c r="L2" s="1" t="n"/>
-      <c r="M2" s="1" t="n"/>
+      <c r="C2" s="5" t="n"/>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+      <c r="H2" s="5" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="5" t="n"/>
+      <c r="K2" s="5" t="n"/>
+      <c r="L2" s="5" t="n"/>
+      <c r="M2" s="5" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -716,23 +736,23 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n"/>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="A6" s="5" t="n"/>
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>CIS HOST BASELINE</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n"/>
-      <c r="D6" s="1" t="n"/>
-      <c r="E6" s="1" t="n"/>
-      <c r="F6" s="1" t="n"/>
-      <c r="G6" s="1" t="n"/>
-      <c r="H6" s="1" t="n"/>
-      <c r="I6" s="1" t="n"/>
-      <c r="J6" s="1" t="n"/>
-      <c r="K6" s="1" t="n"/>
-      <c r="L6" s="1" t="n"/>
-      <c r="M6" s="1" t="n"/>
+      <c r="C6" s="5" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+      <c r="H6" s="5" t="n"/>
+      <c r="I6" s="5" t="n"/>
+      <c r="J6" s="5" t="n"/>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1462,23 +1482,23 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n"/>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="A20" s="5" t="n"/>
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>DOMAIN CONTROLLER BUILD</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n"/>
-      <c r="D20" s="1" t="n"/>
-      <c r="E20" s="1" t="n"/>
-      <c r="F20" s="1" t="n"/>
-      <c r="G20" s="1" t="n"/>
-      <c r="H20" s="1" t="n"/>
-      <c r="I20" s="1" t="n"/>
-      <c r="J20" s="1" t="n"/>
-      <c r="K20" s="1" t="n"/>
-      <c r="L20" s="1" t="n"/>
-      <c r="M20" s="1" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="5" t="n"/>
+      <c r="J20" s="5" t="n"/>
+      <c r="K20" s="5" t="n"/>
+      <c r="L20" s="5" t="n"/>
+      <c r="M20" s="5" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1814,23 +1834,23 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n"/>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="A27" s="5" t="n"/>
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>MEMBER SERVER BUILD</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n"/>
-      <c r="D27" s="1" t="n"/>
-      <c r="E27" s="1" t="n"/>
-      <c r="F27" s="1" t="n"/>
-      <c r="G27" s="1" t="n"/>
-      <c r="H27" s="1" t="n"/>
-      <c r="I27" s="1" t="n"/>
-      <c r="J27" s="1" t="n"/>
-      <c r="K27" s="1" t="n"/>
-      <c r="L27" s="1" t="n"/>
-      <c r="M27" s="1" t="n"/>
+      <c r="C27" s="5" t="n"/>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="5" t="n"/>
+      <c r="J27" s="5" t="n"/>
+      <c r="K27" s="5" t="n"/>
+      <c r="L27" s="5" t="n"/>
+      <c r="M27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1944,23 +1964,23 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n"/>
-      <c r="B30" s="1" t="inlineStr">
+      <c r="A30" s="5" t="n"/>
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>PRIVILEGE ESCALATION</t>
         </is>
       </c>
-      <c r="C30" s="1" t="n"/>
-      <c r="D30" s="1" t="n"/>
-      <c r="E30" s="1" t="n"/>
-      <c r="F30" s="1" t="n"/>
-      <c r="G30" s="1" t="n"/>
-      <c r="H30" s="1" t="n"/>
-      <c r="I30" s="1" t="n"/>
-      <c r="J30" s="1" t="n"/>
-      <c r="K30" s="1" t="n"/>
-      <c r="L30" s="1" t="n"/>
-      <c r="M30" s="1" t="n"/>
+      <c r="C30" s="5" t="n"/>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="5" t="n"/>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -2586,23 +2606,23 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n"/>
-      <c r="B42" s="1" t="inlineStr">
+      <c r="A42" s="5" t="n"/>
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>PERSISTENCE</t>
         </is>
       </c>
-      <c r="C42" s="1" t="n"/>
-      <c r="D42" s="1" t="n"/>
-      <c r="E42" s="1" t="n"/>
-      <c r="F42" s="1" t="n"/>
-      <c r="G42" s="1" t="n"/>
-      <c r="H42" s="1" t="n"/>
-      <c r="I42" s="1" t="n"/>
-      <c r="J42" s="1" t="n"/>
-      <c r="K42" s="1" t="n"/>
-      <c r="L42" s="1" t="n"/>
-      <c r="M42" s="1" t="n"/>
+      <c r="C42" s="5" t="n"/>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+      <c r="H42" s="5" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="5" t="n"/>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2747,23 +2767,23 @@
       <c r="M45" s="2" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n"/>
-      <c r="B46" s="1" t="inlineStr">
+      <c r="A46" s="5" t="n"/>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>CREDENTIAL ACCESS</t>
         </is>
       </c>
-      <c r="C46" s="1" t="n"/>
-      <c r="D46" s="1" t="n"/>
-      <c r="E46" s="1" t="n"/>
-      <c r="F46" s="1" t="n"/>
-      <c r="G46" s="1" t="n"/>
-      <c r="H46" s="1" t="n"/>
-      <c r="I46" s="1" t="n"/>
-      <c r="J46" s="1" t="n"/>
-      <c r="K46" s="1" t="n"/>
-      <c r="L46" s="1" t="n"/>
-      <c r="M46" s="1" t="n"/>
+      <c r="C46" s="5" t="n"/>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+      <c r="H46" s="5" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2904,69 +2924,73 @@
       <c r="M49" s="2" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n"/>
-      <c r="B50" s="1" t="inlineStr">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n"/>
+      <c r="E50" s="2" t="n"/>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Credential Access – Clipboard</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>[Section]: Credential Access
+[Role]: All
+[Expected / Guidance]: Inspect clipboard for credentials if in engagement scope.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="n"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t># Manual only: [Windows.Clipboard]::GetText() with customer approval</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>T1115 - Clipboard Data
+T1552.001 - Credentials In Files</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="n"/>
+      <c r="L50" s="2" t="n"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>Not auto-collected by WinBuildReviewv1.ps1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="n"/>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>LATERAL MOVEMENT</t>
         </is>
       </c>
-      <c r="C50" s="1" t="n"/>
-      <c r="D50" s="1" t="n"/>
-      <c r="E50" s="1" t="n"/>
-      <c r="F50" s="1" t="n"/>
-      <c r="G50" s="1" t="n"/>
-      <c r="H50" s="1" t="n"/>
-      <c r="I50" s="1" t="n"/>
-      <c r="J50" s="1" t="n"/>
-      <c r="K50" s="1" t="n"/>
-      <c r="L50" s="1" t="n"/>
-      <c r="M50" s="1" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="n"/>
-      <c r="E51" s="2" t="n"/>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>Lateral Movement – Shares</t>
-        </is>
-      </c>
-      <c r="G51" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: Lateral Movement
-[Role]: All
-[Expected / Guidance]: No sensitive shares with Everyone Full Control.</t>
-        </is>
-      </c>
-      <c r="H51" s="2" t="n"/>
-      <c r="I51" s="2" t="inlineStr">
-        <is>
-          <t>net share</t>
-        </is>
-      </c>
-      <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>T1021.002 - SMB/Windows Admin Shares
-T1135 - Network Share Discovery</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="n"/>
-      <c r="L51" s="2" t="n"/>
-      <c r="M51" s="2" t="n"/>
+      <c r="C51" s="5" t="n"/>
+      <c r="D51" s="5" t="n"/>
+      <c r="E51" s="5" t="n"/>
+      <c r="F51" s="5" t="n"/>
+      <c r="G51" s="5" t="n"/>
+      <c r="H51" s="5" t="n"/>
+      <c r="I51" s="5" t="n"/>
+      <c r="J51" s="5" t="n"/>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2988,26 +3012,26 @@
       <c r="E52" s="2" t="n"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Lateral Movement – Local Administrators</t>
+          <t>Lateral Movement – Shares</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
           <t>[Section]: Lateral Movement
 [Role]: All
-[Expected / Guidance]: Minimal, documented local admin membership.</t>
+[Expected / Guidance]: No sensitive shares with Everyone Full Control.</t>
         </is>
       </c>
       <c r="H52" s="2" t="n"/>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>net localgroup Administrators</t>
+          <t>net share</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>T1078.003 - Local Accounts
-T1021.002 - SMB/Windows Admin Shares</t>
+          <t>T1021.002 - SMB/Windows Admin Shares
+T1135 - Network Share Discovery</t>
         </is>
       </c>
       <c r="K52" s="2" t="n"/>
@@ -3015,73 +3039,69 @@
       <c r="M52" s="2" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="1" t="inlineStr">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n"/>
+      <c r="E53" s="2" t="n"/>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Lateral Movement – Local Administrators</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>[Section]: Lateral Movement
+[Role]: All
+[Expected / Guidance]: Minimal, documented local admin membership.</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="n"/>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>net localgroup Administrators</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>T1078.003 - Local Accounts
+T1021.002 - SMB/Windows Admin Shares</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="n"/>
+      <c r="L53" s="2" t="n"/>
+      <c r="M53" s="2" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="n"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>DISCOVERY</t>
         </is>
       </c>
-      <c r="C53" s="1" t="n"/>
-      <c r="D53" s="1" t="n"/>
-      <c r="E53" s="1" t="n"/>
-      <c r="F53" s="1" t="n"/>
-      <c r="G53" s="1" t="n"/>
-      <c r="H53" s="1" t="n"/>
-      <c r="I53" s="1" t="n"/>
-      <c r="J53" s="1" t="n"/>
-      <c r="K53" s="1" t="n"/>
-      <c r="L53" s="1" t="n"/>
-      <c r="M53" s="1" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="n"/>
-      <c r="E54" s="2" t="n"/>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>Discovery – Firewall Rules</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: Discovery
-[Role]: All
-[Expected / Guidance]: No unexpected inbound Allow rules on public profile.</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>Get-NetFirewallRule -Enabled True | Select-Object DisplayName, Direction, Action, Profile | Select-Object -First 40</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>T1046 - Network Service Discovery
-T1016 - System Network Configuration Discovery</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>Prefer Get-NetFirewallRule over full netsh dump (performance).</t>
-        </is>
-      </c>
+      <c r="C54" s="5" t="n"/>
+      <c r="D54" s="5" t="n"/>
+      <c r="E54" s="5" t="n"/>
+      <c r="F54" s="5" t="n"/>
+      <c r="G54" s="5" t="n"/>
+      <c r="H54" s="5" t="n"/>
+      <c r="I54" s="5" t="n"/>
+      <c r="J54" s="5" t="n"/>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3103,31 +3123,35 @@
       <c r="E55" s="2" t="n"/>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Discovery – Drive ACL (C:)</t>
+          <t>Discovery – Firewall Rules</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
           <t>[Section]: Discovery
 [Role]: All
-[Expected / Guidance]: Non-admins should not have Modify on C:\ root.</t>
+[Expected / Guidance]: No unexpected inbound Allow rules on public profile.</t>
         </is>
       </c>
       <c r="H55" s="2" t="n"/>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Get-Acl C:\ | Select-Object -ExpandProperty Access</t>
+          <t>Get-NetFirewallRule -Enabled True | Select-Object DisplayName, Direction, Action, Profile | Select-Object -First 40</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>T1083 - File and Directory Discovery
-T1222.001 - Windows Permissions</t>
+          <t>T1046 - Network Service Discovery
+T1016 - System Network Configuration Discovery</t>
         </is>
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="n"/>
-      <c r="M55" s="2" t="n"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>Prefer Get-NetFirewallRule over full netsh dump (performance).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3149,26 +3173,26 @@
       <c r="E56" s="2" t="n"/>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Discovery – Proxy Settings</t>
+          <t>Discovery – Drive ACL (C:)</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
           <t>[Section]: Discovery
 [Role]: All
-[Expected / Guidance]: Expected corporate proxy only.</t>
+[Expected / Guidance]: Non-admins should not have Modify on C:\ root.</t>
         </is>
       </c>
       <c r="H56" s="2" t="n"/>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>netsh winhttp show proxy</t>
+          <t>Get-Acl C:\ | Select-Object -ExpandProperty Access</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>T1090.001 - Internal Proxy
-T1016 - System Network Configuration Discovery</t>
+          <t>T1083 - File and Directory Discovery
+T1222.001 - Windows Permissions</t>
         </is>
       </c>
       <c r="K56" s="2" t="n"/>
@@ -3176,126 +3200,117 @@
       <c r="M56" s="2" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="1" t="inlineStr">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n"/>
+      <c r="E57" s="2" t="n"/>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>Discovery – Proxy Settings</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>[Section]: Discovery
+[Role]: All
+[Expected / Guidance]: Expected corporate proxy only.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="n"/>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>netsh winhttp show proxy</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr">
+        <is>
+          <t>T1090.001 - Internal Proxy
+T1016 - System Network Configuration Discovery</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="n"/>
+      <c r="L57" s="2" t="n"/>
+      <c r="M57" s="2" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="n"/>
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>SYSTEM &amp; DOMAIN</t>
         </is>
       </c>
-      <c r="C57" s="1" t="n"/>
-      <c r="D57" s="1" t="n"/>
-      <c r="E57" s="1" t="n"/>
-      <c r="F57" s="1" t="n"/>
-      <c r="G57" s="1" t="n"/>
-      <c r="H57" s="1" t="n"/>
-      <c r="I57" s="1" t="n"/>
-      <c r="J57" s="1" t="n"/>
-      <c r="K57" s="1" t="n"/>
-      <c r="L57" s="1" t="n"/>
-      <c r="M57" s="1" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="n"/>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="C58" s="5" t="n"/>
+      <c r="D58" s="5" t="n"/>
+      <c r="E58" s="5" t="n"/>
+      <c r="F58" s="5" t="n"/>
+      <c r="G58" s="5" t="n"/>
+      <c r="H58" s="5" t="n"/>
+      <c r="I58" s="5" t="n"/>
+      <c r="J58" s="5" t="n"/>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n"/>
+      <c r="E59" s="2" t="n"/>
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>GPO Summary</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
 [Expected / Guidance]: Expected baseline GPOs applied; no denied CSE errors.</t>
         </is>
       </c>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="inlineStr">
+      <c r="H59" s="2" t="n"/>
+      <c r="I59" s="2" t="inlineStr">
         <is>
           <t>gpresult /r</t>
         </is>
       </c>
-      <c r="J58" s="2" t="inlineStr">
+      <c r="J59" s="2" t="inlineStr">
         <is>
           <t>T1615 - Group Policy Discovery
 T1484.001 - Group Policy Modification</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>Use gpresult /h for HTML on engagements.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="n"/>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: rdp</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>RDP Access Audit</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: System &amp; Domain
-[Role]: All
-[Min OS Profile]: 2012
-[Expected / Guidance]: fDenyTSConnections=1 unless RDP required; NLA (UserAuthentication=1).</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="n"/>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server' -Name fDenyTSConnections -ErrorAction SilentlyContinue; Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server\WinStations\RDP-Tcp' -Name UserAuthentication -ErrorAction SilentlyContinue</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>T1021.001 - Remote Desktop Protocol
-T1563.002 - RDP Hijacking</t>
         </is>
       </c>
       <c r="K59" s="2" t="n"/>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>[CIS Refs]: 2012=18.4.9 / 18.4.10; 2012 R2=18.4.9 / 18.4.10; 2016=18.4.9 / 18.4.10; 2019=18.4.9 / 18.4.10; 2022=18.4.9 / 18.4.10; 2025=18.4.9 / 18.4.10</t>
+          <t>Use gpresult /h for HTML on engagements.</t>
         </is>
       </c>
     </row>
@@ -3316,34 +3331,43 @@
         </is>
       </c>
       <c r="D60" s="2" t="n"/>
-      <c r="E60" s="2" t="n"/>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>[Check ID]: rdp</t>
+        </is>
+      </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>User Account Audit – Local Users</t>
+          <t>RDP Access Audit</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: No stale or unexpected enabled local accounts.</t>
+[Min OS Profile]: 2012
+[Expected / Guidance]: fDenyTSConnections=1 unless RDP required; NLA (UserAuthentication=1).</t>
         </is>
       </c>
       <c r="H60" s="2" t="n"/>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Get-LocalUser | Where-Object Enabled | Select-Object Name, LastLogon, PasswordLastSet</t>
+          <t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server' -Name fDenyTSConnections -ErrorAction SilentlyContinue; Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\Terminal Server\WinStations\RDP-Tcp' -Name UserAuthentication -ErrorAction SilentlyContinue</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>T1087.001 - Local Account
-T1078.003 - Local Accounts</t>
+          <t>T1021.001 - Remote Desktop Protocol
+T1563.002 - RDP Hijacking</t>
         </is>
       </c>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
-      <c r="M60" s="2" t="n"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>[CIS Refs]: 2012=18.4.9 / 18.4.10; 2012 R2=18.4.9 / 18.4.10; 2016=18.4.9 / 18.4.10; 2019=18.4.9 / 18.4.10; 2022=18.4.9 / 18.4.10; 2025=18.4.9 / 18.4.10</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3365,26 +3389,26 @@
       <c r="E61" s="2" t="n"/>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Installed Apps</t>
+          <t>User Account Audit – Local Users</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Flag remote access, legacy, or vulnerable software.</t>
+[Expected / Guidance]: No stale or unexpected enabled local accounts.</t>
         </is>
       </c>
       <c r="H61" s="2" t="n"/>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Get-ItemProperty 'HKLM:\Software\Microsoft\Windows\CurrentVersion\Uninstall\*' | Where-Object DisplayName | Select-Object DisplayName, DisplayVersion | Sort-Object DisplayName | Select-Object -First 50</t>
+          <t>Get-LocalUser | Where-Object Enabled | Select-Object Name, LastLogon, PasswordLastSet</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>T1518 - Software Discovery
-T1082 - System Information Discovery</t>
+          <t>T1087.001 - Local Account
+T1078.003 - Local Accounts</t>
         </is>
       </c>
       <c r="K61" s="2" t="n"/>
@@ -3411,20 +3435,20 @@
       <c r="E62" s="2" t="n"/>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Installed Windows Features</t>
+          <t>Installed Apps</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Remove unnecessary roles (IIS, FTP, etc.) unless in scope.</t>
+[Expected / Guidance]: Flag remote access, legacy, or vulnerable software.</t>
         </is>
       </c>
       <c r="H62" s="2" t="n"/>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>if (Get-Command Get-WindowsFeature -ErrorAction SilentlyContinue) { Get-WindowsFeature | Where-Object Installed | Select-Object Name, DisplayName } else { Get-WindowsOptionalFeature -Online | Where-Object State -eq Enabled | Select-Object FeatureName }</t>
+          <t>Get-ItemProperty 'HKLM:\Software\Microsoft\Windows\CurrentVersion\Uninstall\*' | Where-Object DisplayName | Select-Object DisplayName, DisplayVersion | Sort-Object DisplayName | Select-Object -First 50</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
@@ -3435,11 +3459,7 @@
       </c>
       <c r="K62" s="2" t="n"/>
       <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>Requires elevation on server OS.</t>
-        </is>
-      </c>
+      <c r="M62" s="2" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3458,41 +3478,36 @@
         </is>
       </c>
       <c r="D63" s="2" t="n"/>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: applocker</t>
-        </is>
-      </c>
+      <c r="E63" s="2" t="n"/>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>AppLocker Policy</t>
+          <t>Installed Windows Features</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Min OS Profile]: 2012R2
-[Expected / Guidance]: Effective AppLocker or WDAC policy on hardened builds.</t>
+[Expected / Guidance]: Remove unnecessary roles (IIS, FTP, etc.) unless in scope.</t>
         </is>
       </c>
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>try { Get-AppLockerPolicy -Effective -Xml | Out-String | Select-Object -First 1 } catch { 'AppLocker not configured or not available' }</t>
+          <t>if (Get-Command Get-WindowsFeature -ErrorAction SilentlyContinue) { Get-WindowsFeature | Where-Object Installed | Select-Object Name, DisplayName } else { Get-WindowsOptionalFeature -Online | Where-Object State -eq Enabled | Select-Object FeatureName }</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>T1480 - Execution Guardrails
-T1218 - System Binary Proxy Execution</t>
+          <t>T1518 - Software Discovery
+T1082 - System Information Discovery</t>
         </is>
       </c>
       <c r="K63" s="2" t="n"/>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>[CIS Refs]: 2012=N/A; 2012 R2=18.4.2; 2016=18.4.2; 2019=18.4.2; 2022=18.4.2; 2025=18.4.2</t>
+          <t>Requires elevation on server OS.</t>
         </is>
       </c>
     </row>
@@ -3515,39 +3530,39 @@
       <c r="D64" s="2" t="n"/>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>[Check ID]: device-guard</t>
+          <t>[Check ID]: applocker</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Device Guard / Credential Guard</t>
+          <t>AppLocker Policy</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Min OS Profile]: 2016
-[Expected / Guidance]: VBS/Credential Guard running on high-security builds.</t>
+[Min OS Profile]: 2012R2
+[Expected / Guidance]: Effective AppLocker or WDAC policy on hardened builds.</t>
         </is>
       </c>
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Get-CimInstance -Namespace root\Microsoft\Windows\DeviceGuard -ClassName DeviceGuard -ErrorAction SilentlyContinue | Select-Object SecurityServicesConfigured, SecurityServicesRunning, VirtualizationBasedSecurityStatus</t>
+          <t>try { Get-AppLockerPolicy -Effective -Xml | Out-String | Select-Object -First 1 } catch { 'AppLocker not configured or not available' }</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>T1003.001 - LSASS Memory
-T1055 - Process Injection</t>
+          <t>T1480 - Execution Guardrails
+T1218 - System Binary Proxy Execution</t>
         </is>
       </c>
       <c r="K64" s="2" t="n"/>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>[CIS Refs]: 2012=N/A; 2012 R2=N/A; 2016=18.5.x (Device Guard / VBS); 2019=18.5.x; 2022=18.5.x; 2025=18.5.x</t>
+          <t>[CIS Refs]: 2012=N/A; 2012 R2=18.4.2; 2016=18.4.2; 2019=18.4.2; 2022=18.4.2; 2025=18.4.2</t>
         </is>
       </c>
     </row>
@@ -3568,36 +3583,41 @@
         </is>
       </c>
       <c r="D65" s="2" t="n"/>
-      <c r="E65" s="2" t="n"/>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>[Check ID]: device-guard</t>
+        </is>
+      </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Domain Membership</t>
+          <t>Device Guard / Credential Guard</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: DomainRole 4/5 = DC; 3 = member server; 0-2 = standalone.</t>
+[Min OS Profile]: 2016
+[Expected / Guidance]: VBS/Credential Guard running on high-security builds.</t>
         </is>
       </c>
       <c r="H65" s="2" t="n"/>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>nltest /dsgetdc:$env:USERDOMAIN 2&gt;&amp;1; (Get-CimInstance Win32_ComputerSystem).DomainRole</t>
+          <t>Get-CimInstance -Namespace root\Microsoft\Windows\DeviceGuard -ClassName DeviceGuard -ErrorAction SilentlyContinue | Select-Object SecurityServicesConfigured, SecurityServicesRunning, VirtualizationBasedSecurityStatus</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>T1087.002 - Domain Account
-T1482 - Domain Trust Discovery</t>
+          <t>T1003.001 - LSASS Memory
+T1055 - Process Injection</t>
         </is>
       </c>
       <c r="K65" s="2" t="n"/>
       <c r="L65" s="2" t="n"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>Used by runner to select DC vs MS checks.</t>
+          <t>[CIS Refs]: 2012=N/A; 2012 R2=N/A; 2016=18.5.x (Device Guard / VBS); 2019=18.5.x; 2022=18.5.x; 2025=18.5.x</t>
         </is>
       </c>
     </row>
@@ -3621,31 +3641,35 @@
       <c r="E66" s="2" t="n"/>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Time Sync Status</t>
+          <t>Domain Membership</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Syncing to valid source; low clock skew.</t>
+[Expected / Guidance]: DomainRole 4/5 = DC; 3 = member server; 0-2 = standalone.</t>
         </is>
       </c>
       <c r="H66" s="2" t="n"/>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>w32tm /query /status</t>
+          <t>nltest /dsgetdc:$env:USERDOMAIN 2&gt;&amp;1; (Get-CimInstance Win32_ComputerSystem).DomainRole</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>T1082 - System Information Discovery
-T1016 - System Network Configuration Discovery</t>
+          <t>T1087.002 - Domain Account
+T1482 - Domain Trust Discovery</t>
         </is>
       </c>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
-      <c r="M66" s="2" t="n"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>Used by runner to select DC vs MS checks.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3667,26 +3691,26 @@
       <c r="E67" s="2" t="n"/>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>DNS Configuration</t>
+          <t>Time Sync Status</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Internal DNS on domain members; not public-only resolvers.</t>
+[Expected / Guidance]: Syncing to valid source; low clock skew.</t>
         </is>
       </c>
       <c r="H67" s="2" t="n"/>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Get-DnsClientServerAddress -AddressFamily IPv4 | Select-Object InterfaceAlias, ServerAddresses</t>
+          <t>w32tm /query /status</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>T1016 - System Network Configuration Discovery
-T1590.002 - DNS</t>
+          <t>T1082 - System Information Discovery
+T1016 - System Network Configuration Discovery</t>
         </is>
       </c>
       <c r="K67" s="2" t="n"/>
@@ -3713,54 +3737,81 @@
       <c r="E68" s="2" t="n"/>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Security Logs Sample</t>
+          <t>DNS Configuration</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Security log accessible; recent audit events present.</t>
+[Expected / Guidance]: Internal DNS on domain members; not public-only resolvers.</t>
         </is>
       </c>
       <c r="H68" s="2" t="n"/>
       <c r="I68" s="2" t="inlineStr">
         <is>
+          <t>Get-DnsClientServerAddress -AddressFamily IPv4 | Select-Object InterfaceAlias, ServerAddresses</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr">
+        <is>
+          <t>T1016 - System Network Configuration Discovery
+T1590.002 - DNS</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="n"/>
+      <c r="L68" s="2" t="n"/>
+      <c r="M68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n"/>
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Security Logs Sample</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>[Section]: System &amp; Domain
+[Role]: All
+[Expected / Guidance]: Security log accessible; recent audit events present.</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
           <t>Get-WinEvent -LogName Security -MaxEvents 15 -ErrorAction SilentlyContinue | Select-Object TimeCreated, Id, LevelDisplayName, Message</t>
         </is>
       </c>
-      <c r="J68" s="2" t="inlineStr">
+      <c r="J69" s="2" t="inlineStr">
         <is>
           <t>T1654 - Log Enumeration
 T1070.001 - Clear Windows Event Logs</t>
         </is>
       </c>
-      <c r="K68" s="2" t="n"/>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="inlineStr">
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="inlineStr">
         <is>
           <t>Requires appropriate log read rights.</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>CREDENTIAL ACCESS</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="n"/>
-      <c r="D69" s="1" t="n"/>
-      <c r="E69" s="1" t="n"/>
-      <c r="F69" s="1" t="n"/>
-      <c r="G69" s="1" t="n"/>
-      <c r="H69" s="1" t="n"/>
-      <c r="I69" s="1" t="n"/>
-      <c r="J69" s="1" t="n"/>
-      <c r="K69" s="1" t="n"/>
-      <c r="L69" s="1" t="n"/>
-      <c r="M69" s="1" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3782,25 +3833,25 @@
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Credential Access – Clipboard</t>
+          <t>System Info – Environment Variables</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>[Section]: Credential Access
-[Role]: All
-[Expected / Guidance]: Inspect clipboard for credentials if in engagement scope.</t>
+          <t>[Section]: System &amp; Domain
+[Role]: All
+[Expected / Guidance]: Review for secrets in environment.</t>
         </is>
       </c>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t># Manual only: [Windows.Clipboard]::GetText() with customer approval</t>
+          <t>Get-ChildItem Env: | Select-Object Name, Value -First 30</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>T1115 - Clipboard Data
+          <t>T1082 - System Information Discovery
 T1552.001 - Credentials In Files</t>
         </is>
       </c>
@@ -3808,28 +3859,55 @@
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Not auto-collected by WinBuildReviewv1.ps1.</t>
+          <t>Script filters names matching PASSWORD/SECRET/TOKEN.</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n"/>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>SYSTEM &amp; DOMAIN</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="n"/>
-      <c r="D71" s="1" t="n"/>
-      <c r="E71" s="1" t="n"/>
-      <c r="F71" s="1" t="n"/>
-      <c r="G71" s="1" t="n"/>
-      <c r="H71" s="1" t="n"/>
-      <c r="I71" s="1" t="n"/>
-      <c r="J71" s="1" t="n"/>
-      <c r="K71" s="1" t="n"/>
-      <c r="L71" s="1" t="n"/>
-      <c r="M71" s="1" t="n"/>
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Standard</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>In Scope</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Pentester</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n"/>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>App Crash Logs</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>[Section]: System &amp; Domain
+[Role]: All
+[Expected / Guidance]: Recent application crashes reviewed.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Get-WinEvent -FilterHashtable @{ LogName='Application'; Id=1000,1001; StartTime=(Get-Date).AddDays(-30) } -MaxEvents 10</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr">
+        <is>
+          <t>T1654 - Log Enumeration
+T1082 - System Information Discovery</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3848,28 +3926,33 @@
         </is>
       </c>
       <c r="D72" s="2" t="n"/>
-      <c r="E72" s="2" t="n"/>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>[Check ID]: crash-dump</t>
+        </is>
+      </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>System Info – Environment Variables</t>
+          <t>Crash Dump Settings</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Review for secrets in environment.</t>
+[Min OS Profile]: 2012
+[Expected / Guidance]: Full memory dumps disabled unless required.</t>
         </is>
       </c>
       <c r="H72" s="2" t="n"/>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Get-ChildItem Env: | Select-Object Name, Value -First 30</t>
+          <t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\CrashControl' -ErrorAction SilentlyContinue</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>T1082 - System Information Discovery
+          <t>T1003.001 - LSASS Memory
 T1552.001 - Credentials In Files</t>
         </is>
       </c>
@@ -3877,7 +3960,7 @@
       <c r="L72" s="2" t="n"/>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Script filters names matching PASSWORD/SECRET/TOKEN.</t>
+          <t>[CIS Refs]: 2012=18.5.1; 2012 R2=18.5.1; 2016=18.5.1; 2019=18.5.1; 2022=18.5.1; 2025=18.5.1</t>
         </is>
       </c>
     </row>
@@ -3898,469 +3981,41 @@
         </is>
       </c>
       <c r="D73" s="2" t="n"/>
-      <c r="E73" s="2" t="n"/>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>[Check ID]: wsl-presence</t>
+        </is>
+      </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>App Crash Logs</t>
+          <t>Defense Evasion – WSL Presence</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
           <t>[Section]: System &amp; Domain
 [Role]: All
-[Expected / Guidance]: Recent application crashes reviewed.</t>
+[Min OS Profile]: 2022
+[Expected / Guidance]: Document WSL if present on server builds.</t>
         </is>
       </c>
       <c r="H73" s="2" t="n"/>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Get-WinEvent -FilterHashtable @{ LogName='Application'; Id=1000,1001; StartTime=(Get-Date).AddDays(-30) } -MaxEvents 10</t>
+          <t>Test-Path "C:\Windows\System32\bash.exe"; Test-Path "C:\Windows\System32\wsl.exe"</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>T1654 - Log Enumeration
-T1082 - System Information Discovery</t>
+          <t>T1211 - Exploitation for Stealth
+T1059.003 - Windows Command Shell</t>
         </is>
       </c>
       <c r="K73" s="2" t="n"/>
       <c r="L73" s="2" t="n"/>
-      <c r="M73" s="2" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="n"/>
-      <c r="E74" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: crash-dump</t>
-        </is>
-      </c>
-      <c r="F74" s="2" t="inlineStr">
-        <is>
-          <t>Crash Dump Settings</t>
-        </is>
-      </c>
-      <c r="G74" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: System &amp; Domain
-[Role]: All
-[Min OS Profile]: 2012
-[Expected / Guidance]: Full memory dumps disabled unless required.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="n"/>
-      <c r="I74" s="2" t="inlineStr">
-        <is>
-          <t>Get-ItemProperty 'HKLM:\SYSTEM\CurrentControlSet\Control\CrashControl' -ErrorAction SilentlyContinue</t>
-        </is>
-      </c>
-      <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>T1003.001 - LSASS Memory
-T1552.001 - Credentials In Files</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="n"/>
-      <c r="L74" s="2" t="n"/>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>[CIS Refs]: 2012=18.5.1; 2012 R2=18.5.1; 2016=18.5.1; 2019=18.5.1; 2022=18.5.1; 2025=18.5.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="n"/>
-      <c r="E75" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: wsl-presence</t>
-        </is>
-      </c>
-      <c r="F75" s="2" t="inlineStr">
-        <is>
-          <t>Defense Evasion – WSL Presence</t>
-        </is>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: System &amp; Domain
-[Role]: All
-[Min OS Profile]: 2022
-[Expected / Guidance]: Document WSL if present on server builds.</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="n"/>
-      <c r="I75" s="2" t="inlineStr">
-        <is>
-          <t>Test-Path "C:\Windows\System32\bash.exe"; Test-Path "C:\Windows\System32\wsl.exe"</t>
-        </is>
-      </c>
-      <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>T1211 - Exploitation for Stealth
-T1059.003 - Windows Command Shell</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="n"/>
-      <c r="L75" s="2" t="n"/>
-      <c r="M75" s="2" t="inlineStr">
+      <c r="M73" s="2" t="inlineStr">
         <is>
           <t>[CIS Refs]: 2012=N/A (pentest); 2012 R2=N/A (pentest); 2016=N/A (pentest); 2019=N/A (pentest); 2022=N/A (pentest); 2025=N/A (pentest)</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="1" t="n"/>
-      <c r="B76" s="1" t="inlineStr">
-        <is>
-          <t>PRIVESC</t>
-        </is>
-      </c>
-      <c r="C76" s="1" t="n"/>
-      <c r="D76" s="1" t="n"/>
-      <c r="E76" s="1" t="n"/>
-      <c r="F76" s="1" t="n"/>
-      <c r="G76" s="1" t="n"/>
-      <c r="H76" s="1" t="n"/>
-      <c r="I76" s="1" t="n"/>
-      <c r="J76" s="1" t="n"/>
-      <c r="K76" s="1" t="n"/>
-      <c r="L76" s="1" t="n"/>
-      <c r="M76" s="1" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="n"/>
-      <c r="E77" s="2" t="n"/>
-      <c r="F77" s="2" t="inlineStr">
-        <is>
-          <t>PrivEsc – Services</t>
-        </is>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: PrivEsc
-[Role]: All
-[Expected / Guidance]: Follow up with ACL checks on path</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t>WinBuildReview.ps1 (WinBuildReview.PrivEscDeep.ps1)</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t>Get-WmiObject Win32_Service | Where-Object { $_.PathName -notmatch '"' }</t>
-        </is>
-      </c>
-      <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>T1574.009 - Path Interception by Unquoted Path
-T1543.003 - Windows Service</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="n"/>
-      <c r="L77" s="2" t="n"/>
-      <c r="M77" s="2" t="inlineStr">
-        <is>
-          <t>Imported from source; example: ServiceName: AppService; Path: C:\Program Files\App\app.exe</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="n"/>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="inlineStr">
-        <is>
-          <t>PrivEsc – ACLs</t>
-        </is>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: PrivEsc
-[Role]: All
-[Expected / Guidance]: Recursively check subfolders</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t>WinBuildReview.ps1 (WinBuildReview.PrivEscDeep.ps1)</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr">
-        <is>
-          <t>Get-Acl "C:\Program Files"</t>
-        </is>
-      </c>
-      <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>T1574.010 - Services File Permissions Weakness
-T1222.001 - Windows Permissions</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="inlineStr">
-        <is>
-          <t>Imported from source; example: User 'Everyone' has 'Write' access</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="1" t="n"/>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>DISCOVERY</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="n"/>
-      <c r="D79" s="1" t="n"/>
-      <c r="E79" s="1" t="n"/>
-      <c r="F79" s="1" t="n"/>
-      <c r="G79" s="1" t="n"/>
-      <c r="H79" s="1" t="n"/>
-      <c r="I79" s="1" t="n"/>
-      <c r="J79" s="1" t="n"/>
-      <c r="K79" s="1" t="n"/>
-      <c r="L79" s="1" t="n"/>
-      <c r="M79" s="1" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="n"/>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="inlineStr">
-        <is>
-          <t>Discovery – Drive ACL</t>
-        </is>
-      </c>
-      <c r="G80" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: Discovery
-[Role]: All
-[Expected / Guidance]: Should restrict non-admin write access</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="inlineStr">
-        <is>
-          <t>Get-Acl C:\</t>
-        </is>
-      </c>
-      <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>T1083 - File and Directory Discovery
-T1222.001 - Windows Permissions</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="2" t="inlineStr">
-        <is>
-          <t>Imported from source; example: 'Everyone' has Modify access</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="1" t="n"/>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>LEGACY</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="n"/>
-      <c r="D81" s="1" t="n"/>
-      <c r="E81" s="1" t="n"/>
-      <c r="F81" s="1" t="n"/>
-      <c r="G81" s="1" t="n"/>
-      <c r="H81" s="1" t="n"/>
-      <c r="I81" s="1" t="n"/>
-      <c r="J81" s="1" t="n"/>
-      <c r="K81" s="1" t="n"/>
-      <c r="L81" s="1" t="n"/>
-      <c r="M81" s="1" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="n"/>
-      <c r="E82" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: runasppl</t>
-        </is>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>LSASS Protection Status</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: Legacy
-[Role]: All
-[Min OS Profile]: 2016
-[Expected / Guidance]: Blocks dumping techniques like Mimikatz</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="n"/>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>reg query HKLM\SYSTEM\CurrentControlSet\Control\Lsa /v RunAsPPL</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>T1003.001 - LSASS Memory
-T1562.001 - Disable or Modify Tools</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="n"/>
-      <c r="L82" s="2" t="n"/>
-      <c r="M82" s="2" t="inlineStr">
-        <is>
-          <t>[CIS Refs]: 2012=N/A; 2012 R2=N/A; 2016=18.4.7 (RunAsPPL advisory); 2019=18.4.7; 2022=18.4.7; 2025=18.4.7
-Imported from source; example: RunAsPPL    REG_DWORD    0x1</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
-        <is>
-          <t>Standard</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>In Scope</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Pentester</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="n"/>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>[Check ID]: password-policy</t>
-        </is>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Password Policy Audit</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>[Section]: Legacy
-[Role]: All
-[Min OS Profile]: 2012
-[Expected / Guidance]: Use Get-ADDefaultDomainPasswordPolicy on</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="n"/>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>net accounts</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>T1201 - Password Policy Discovery
-T1110 - Brute Force</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="n"/>
-      <c r="L83" s="2" t="n"/>
-      <c r="M83" s="2" t="inlineStr">
-        <is>
-          <t>[CIS Refs]: 2012=1.1.1 / 1.2.1; 2012 R2=1.1.x / 1.2.x; 2016=1.1.x / 1.2.x; 2019=1.1.x / 1.2.x; 2022=1.1.x / 1.2.x; 2025=1.1.x / 1.2.x
-Imported from source; example: Min password length: 8; Complexity: Enabled</t>
         </is>
       </c>
     </row>
@@ -4385,22 +4040,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="4" t="inlineStr">
         <is>
           <t>OS Profile</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="4" t="inlineStr">
         <is>
           <t>CIS Benchmark PDF</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="4" t="inlineStr">
         <is>
           <t>Version</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="4" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
